--- a/artfynd/A 27518-2024 artfynd.xlsx
+++ b/artfynd/A 27518-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118529897</v>
+        <v>118529896</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
+        <v>79600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718533</v>
+        <v>718486</v>
       </c>
       <c r="R3" t="n">
-        <v>7112745</v>
+        <v>7112667</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -871,17 +871,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118529896</v>
+        <v>118529897</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>5166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718486</v>
+        <v>718533</v>
       </c>
       <c r="R4" t="n">
-        <v>7112667</v>
+        <v>7112745</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -988,17 +988,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 27518-2024 artfynd.xlsx
+++ b/artfynd/A 27518-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118529888</v>
+        <v>118529897</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>5166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718560</v>
+        <v>718533</v>
       </c>
       <c r="R2" t="n">
-        <v>7112715</v>
+        <v>7112745</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,11 +753,6 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre hack, kolad ved (brunnit efter hacken)</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118529896</v>
+        <v>118529888</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718486</v>
+        <v>718560</v>
       </c>
       <c r="R3" t="n">
-        <v>7112667</v>
+        <v>7112715</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,6 +870,11 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre hack, kolad ved (brunnit efter hacken)</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -868,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118529897</v>
+        <v>118529896</v>
       </c>
       <c r="B4" t="n">
-        <v>5166</v>
+        <v>79600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718533</v>
+        <v>718486</v>
       </c>
       <c r="R4" t="n">
-        <v>7112745</v>
+        <v>7112667</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -988,17 +988,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 27518-2024 artfynd.xlsx
+++ b/artfynd/A 27518-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118529897</v>
+        <v>118529888</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718533</v>
+        <v>718560</v>
       </c>
       <c r="R2" t="n">
-        <v>7112745</v>
+        <v>7112715</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,6 +753,11 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre hack, kolad ved (brunnit efter hacken)</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118529888</v>
+        <v>118529896</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718560</v>
+        <v>718486</v>
       </c>
       <c r="R3" t="n">
-        <v>7112715</v>
+        <v>7112667</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -870,11 +860,6 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre hack, kolad ved (brunnit efter hacken)</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118529896</v>
+        <v>118529897</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>5166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718486</v>
+        <v>718533</v>
       </c>
       <c r="R4" t="n">
-        <v>7112667</v>
+        <v>7112745</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -988,17 +988,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 27518-2024 artfynd.xlsx
+++ b/artfynd/A 27518-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118529896</v>
+        <v>118529897</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718486</v>
+        <v>718533</v>
       </c>
       <c r="R3" t="n">
-        <v>7112667</v>
+        <v>7112745</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -871,17 +871,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118529897</v>
+        <v>118529896</v>
       </c>
       <c r="B4" t="n">
-        <v>5166</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718533</v>
+        <v>718486</v>
       </c>
       <c r="R4" t="n">
-        <v>7112745</v>
+        <v>7112667</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -988,17 +988,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
